--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorTargetList" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,10 +81,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text/>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>序号ID</t>
   </si>
@@ -123,6 +123,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>场景ID</t>
+  </si>
+  <si>
     <t>界面显示的个数</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
   </si>
   <si>
     <t>PoolType</t>
+  </si>
+  <si>
+    <t>RegionID</t>
   </si>
   <si>
     <t>DisplayCount</t>
@@ -372,12 +378,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1395,19 +1401,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
-    <col min="5" max="5" width="23.125" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="59.375" customWidth="1"/>
-    <col min="8" max="8" width="20.625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="22.875" customWidth="1"/>
+    <col min="4" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="59.375" customWidth="1"/>
+    <col min="9" max="9" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,20 +1444,23 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
@@ -1460,7 +1469,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>11</v>
@@ -1468,36 +1477,42 @@
       <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1508,8 +1523,9 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1517,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1525,19 +1541,22 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="b">
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1" t="b">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>22</v>
+      <c r="K5" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1545,26 +1564,29 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="b">
+      <c r="G6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="1" t="b">
+      <c r="H6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>25</v>
+      <c r="K6" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="VisitorTargetList" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,9 +83,32 @@
       </text>
     </comment>
     <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-1或空值表示没有观看次数；
+填写值为具体的观看次数上限值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
       <text/>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>序号ID</t>
   </si>
@@ -135,6 +159,9 @@
     <t>是否每日刷新</t>
   </si>
   <si>
+    <t>单日观看次数上限</t>
+  </si>
+  <si>
     <t>手动刷新的费用</t>
   </si>
   <si>
@@ -174,6 +201,9 @@
     <t>DailyRefresh</t>
   </si>
   <si>
+    <t>DailyViewLimit</t>
+  </si>
+  <si>
     <t>RefreshCost</t>
   </si>
   <si>
@@ -186,7 +216,7 @@
     <t>广告卡池</t>
   </si>
   <si>
-    <t>1001_300|1002_300|1003_300|1004_300|1005_300</t>
+    <t>1025101_300|1025102_300|1025103_300|1025104_300|1025105_300|1025106_300|1025201_200|1025202_200|1025203_200|1025204_200|1025205_200|1025206_200|1025301_100|1025302_100|1025303_100|1025304_100|1025305_100|1025306_100</t>
   </si>
   <si>
     <t>付费卡池</t>
@@ -195,7 +225,7 @@
     <t>1980000_0|1980000_20|1980000_30|1980000_40|1980000_50</t>
   </si>
   <si>
-    <t>101_1000|102_1000|103_1000|104_300|105_500|106_500|201_200|202_200|203_200|204_200|205_200</t>
+    <t>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
   </si>
 </sst>
 </file>
@@ -218,12 +248,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -378,12 +408,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -853,17 +883,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1401,192 +1440,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="4" max="5" width="16.375" customWidth="1"/>
     <col min="6" max="6" width="23.125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="59.375" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="22.875" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
+    <col min="9" max="9" width="59.375" customWidth="1"/>
+    <col min="10" max="10" width="20.625" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:11">
-      <c r="A5" s="1">
+      <c r="J3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:12">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="b">
+      <c r="G5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="b">
+      <c r="H5" s="3">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:11">
-      <c r="A6" s="1">
+      <c r="L5" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:12">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="b">
+      <c r="G6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="1" t="b">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>27</v>
+      <c r="L6" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1597,4 +1651,610 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="E5:G60"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="5" spans="5:7">
+      <c r="G5" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G6:G23)</f>
+        <v>1025101_300|1025102_300|1025103_300|1025104_300|1025105_300|1025106_300|1025201_200|1025202_200|1025203_200|1025204_200|1025205_200|1025206_200|1025301_100|1025302_100|1025303_100|1025304_100|1025305_100|1025306_100</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="5:7">
+      <c r="E6" s="1">
+        <v>1025101</v>
+      </c>
+      <c r="F6">
+        <v>300</v>
+      </c>
+      <c r="G6" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,E6,F6)</f>
+        <v>1025101_300</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="5:7">
+      <c r="E7" s="1">
+        <v>1025102</v>
+      </c>
+      <c r="F7">
+        <v>300</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" ref="G7:G23" si="0">_xlfn.TEXTJOIN("_",TRUE,E7,F7)</f>
+        <v>1025102_300</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="5:7">
+      <c r="E8" s="1">
+        <v>1025103</v>
+      </c>
+      <c r="F8">
+        <v>300</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>1025103_300</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="5:7">
+      <c r="E9" s="1">
+        <v>1025104</v>
+      </c>
+      <c r="F9">
+        <v>300</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>1025104_300</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="5:7">
+      <c r="E10" s="1">
+        <v>1025105</v>
+      </c>
+      <c r="F10">
+        <v>300</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>1025105_300</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="5:7">
+      <c r="E11" s="1">
+        <v>1025106</v>
+      </c>
+      <c r="F11">
+        <v>300</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>1025106_300</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="5:7">
+      <c r="E12" s="1">
+        <v>1025201</v>
+      </c>
+      <c r="F12">
+        <v>200</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>1025201_200</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="5:7">
+      <c r="E13" s="1">
+        <v>1025202</v>
+      </c>
+      <c r="F13">
+        <v>200</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>1025202_200</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="5:7">
+      <c r="E14" s="1">
+        <v>1025203</v>
+      </c>
+      <c r="F14">
+        <v>200</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>1025203_200</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="5:7">
+      <c r="E15" s="1">
+        <v>1025204</v>
+      </c>
+      <c r="F15">
+        <v>200</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>1025204_200</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="5:7">
+      <c r="E16" s="1">
+        <v>1025205</v>
+      </c>
+      <c r="F16">
+        <v>200</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>1025205_200</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="5:7">
+      <c r="E17" s="1">
+        <v>1025206</v>
+      </c>
+      <c r="F17">
+        <v>200</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>1025206_200</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="5:7">
+      <c r="E18" s="1">
+        <v>1025301</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>1025301_100</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="5:7">
+      <c r="E19" s="1">
+        <v>1025302</v>
+      </c>
+      <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>1025302_100</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="5:7">
+      <c r="E20" s="1">
+        <v>1025303</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v>1025303_100</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="5:7">
+      <c r="E21" s="1">
+        <v>1025304</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v>1025304_100</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="5:7">
+      <c r="E22" s="1">
+        <v>1025305</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v>1025305_100</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="5:7">
+      <c r="E23" s="1">
+        <v>1025306</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v>1025306_100</v>
+      </c>
+    </row>
+    <row r="30" spans="5:7">
+      <c r="G30" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,G31:G60)</f>
+        <v>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="5:7">
+      <c r="E31" s="2">
+        <v>1025101</v>
+      </c>
+      <c r="F31">
+        <v>500</v>
+      </c>
+      <c r="G31" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,E31,F31)</f>
+        <v>1025101_500</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="5:7">
+      <c r="E32" s="2">
+        <v>1025102</v>
+      </c>
+      <c r="F32">
+        <v>500</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" ref="G32:G60" si="1">_xlfn.TEXTJOIN("_",TRUE,E32,F32)</f>
+        <v>1025102_500</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="5:7">
+      <c r="E33" s="2">
+        <v>1025103</v>
+      </c>
+      <c r="F33">
+        <v>500</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="1"/>
+        <v>1025103_500</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="5:7">
+      <c r="E34" s="2">
+        <v>1025104</v>
+      </c>
+      <c r="F34">
+        <v>500</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="1"/>
+        <v>1025104_500</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="5:7">
+      <c r="E35" s="2">
+        <v>1025105</v>
+      </c>
+      <c r="F35">
+        <v>500</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="1"/>
+        <v>1025105_500</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="5:7">
+      <c r="E36" s="2">
+        <v>1025106</v>
+      </c>
+      <c r="F36">
+        <v>500</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="1"/>
+        <v>1025106_500</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="5:7">
+      <c r="E37" s="2">
+        <v>1025201</v>
+      </c>
+      <c r="F37">
+        <v>400</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="1"/>
+        <v>1025201_400</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="5:7">
+      <c r="E38" s="2">
+        <v>1025202</v>
+      </c>
+      <c r="F38">
+        <v>400</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="1"/>
+        <v>1025202_400</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="5:7">
+      <c r="E39" s="2">
+        <v>1025203</v>
+      </c>
+      <c r="F39">
+        <v>400</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="1"/>
+        <v>1025203_400</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="5:7">
+      <c r="E40" s="2">
+        <v>1025204</v>
+      </c>
+      <c r="F40">
+        <v>400</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="1"/>
+        <v>1025204_400</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="5:7">
+      <c r="E41" s="2">
+        <v>1025205</v>
+      </c>
+      <c r="F41">
+        <v>400</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="1"/>
+        <v>1025205_400</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="5:7">
+      <c r="E42" s="2">
+        <v>1025206</v>
+      </c>
+      <c r="F42">
+        <v>400</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="1"/>
+        <v>1025206_400</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="5:7">
+      <c r="E43" s="2">
+        <v>1025301</v>
+      </c>
+      <c r="F43">
+        <v>300</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="1"/>
+        <v>1025301_300</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="5:7">
+      <c r="E44" s="2">
+        <v>1025302</v>
+      </c>
+      <c r="F44">
+        <v>300</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="1"/>
+        <v>1025302_300</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="5:7">
+      <c r="E45" s="2">
+        <v>1025303</v>
+      </c>
+      <c r="F45">
+        <v>300</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="1"/>
+        <v>1025303_300</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="5:7">
+      <c r="E46" s="2">
+        <v>1025304</v>
+      </c>
+      <c r="F46">
+        <v>300</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="1"/>
+        <v>1025304_300</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="5:7">
+      <c r="E47" s="2">
+        <v>1025305</v>
+      </c>
+      <c r="F47">
+        <v>300</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="1"/>
+        <v>1025305_300</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="5:7">
+      <c r="E48" s="2">
+        <v>1025306</v>
+      </c>
+      <c r="F48">
+        <v>300</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="1"/>
+        <v>1025306_300</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="5:7">
+      <c r="E49" s="2">
+        <v>1025401</v>
+      </c>
+      <c r="F49">
+        <v>200</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="1"/>
+        <v>1025401_200</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="5:7">
+      <c r="E50" s="2">
+        <v>1025402</v>
+      </c>
+      <c r="F50">
+        <v>200</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>1025402_200</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="5:7">
+      <c r="E51" s="2">
+        <v>1025403</v>
+      </c>
+      <c r="F51">
+        <v>200</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v>1025403_200</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="5:7">
+      <c r="E52" s="2">
+        <v>1025404</v>
+      </c>
+      <c r="F52">
+        <v>200</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="1"/>
+        <v>1025404_200</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="5:7">
+      <c r="E53" s="2">
+        <v>1025405</v>
+      </c>
+      <c r="F53">
+        <v>200</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="1"/>
+        <v>1025405_200</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="5:7">
+      <c r="E54" s="2">
+        <v>1025406</v>
+      </c>
+      <c r="F54">
+        <v>200</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>1025406_200</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="5:7">
+      <c r="E55" s="2">
+        <v>1025501</v>
+      </c>
+      <c r="F55">
+        <v>100</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="1"/>
+        <v>1025501_100</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="5:7">
+      <c r="E56" s="2">
+        <v>1025502</v>
+      </c>
+      <c r="F56">
+        <v>100</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="1"/>
+        <v>1025502_100</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="5:7">
+      <c r="E57" s="2">
+        <v>1025503</v>
+      </c>
+      <c r="F57">
+        <v>100</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="1"/>
+        <v>1025503_100</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="5:7">
+      <c r="E58" s="2">
+        <v>1025504</v>
+      </c>
+      <c r="F58">
+        <v>100</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="1"/>
+        <v>1025504_100</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="5:7">
+      <c r="E59" s="2">
+        <v>1025505</v>
+      </c>
+      <c r="F59">
+        <v>100</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="1"/>
+        <v>1025505_100</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="5:7">
+      <c r="E60" s="2">
+        <v>1025506</v>
+      </c>
+      <c r="F60">
+        <v>100</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="1"/>
+        <v>1025506_100</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E6:E23">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E60">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -13,7 +13,8 @@
   </bookViews>
   <sheets>
     <sheet name="VisitorTargetList" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -135,8 +136,111 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+指界面上每个卡池显示几个游客礼包</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+指在礼包中可能出现的游客种类个数</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-1或空值表示没有观看次数；
+填写值为具体的观看次数上限值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text/>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-1或空值表示没有上线；
+具体值时为对应值的次数上限</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t>序号ID</t>
   </si>
@@ -226,6 +330,21 @@
   </si>
   <si>
     <t>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
+  </si>
+  <si>
+    <t>是否按时段刷新</t>
+  </si>
+  <si>
+    <t>每日多长时间刷新一次（H)</t>
+  </si>
+  <si>
+    <t>每个时间段手动刷新的次数上限</t>
+  </si>
+  <si>
+    <t>每次刷新出现的游客购买次数上限</t>
+  </si>
+  <si>
+    <t>1980000_20|1980000_30|1980000_40|1980000_50</t>
   </si>
 </sst>
 </file>
@@ -408,12 +527,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1656,6 +1775,247 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <cols>
+    <col min="4" max="4" width="11.125" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="16.125" customWidth="1"/>
+    <col min="10" max="10" width="16.25" customWidth="1"/>
+    <col min="11" max="11" width="26.5" customWidth="1"/>
+    <col min="12" max="12" width="30.125" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="22.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:14">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:14">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>8</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="3">
+        <v>4</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B5:B6">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="E5:G60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -3,18 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="VisitorTargetList" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="VisitorTargetList" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,109 +28,6 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-指界面上每个卡池显示几个游客礼包</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-指在礼包中可能出现的游客种类个数</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--1或空值表示没有观看次数；
-填写值为具体的观看次数上限值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--1或空值表示没有上线；
-具体值时为对应值的次数上限</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
@@ -210,7 +101,16 @@
       </text>
     </comment>
     <comment ref="J1" authorId="0">
-      <text/>
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>当配置的消耗低于刷新的次数时，配置的最后那个消耗一直重复使用</t>
+        </r>
+      </text>
     </comment>
     <comment ref="K1" authorId="0">
       <text>
@@ -230,7 +130,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
--1或空值表示没有上线；
+-1或空值表示没有上限；
 具体值时为对应值的次数上限</t>
         </r>
       </text>
@@ -240,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>序号ID</t>
   </si>
@@ -260,7 +160,10 @@
     <t>礼包出现游客的种类个数</t>
   </si>
   <si>
-    <t>是否每日刷新</t>
+    <t>是否按时段刷新</t>
+  </si>
+  <si>
+    <t>每日的刷新时间点</t>
   </si>
   <si>
     <t>单日观看次数上限</t>
@@ -269,7 +172,10 @@
     <t>手动刷新的费用</t>
   </si>
   <si>
-    <t>每日刷新的次数上限</t>
+    <t>每个时间段手动刷新的次数上限</t>
+  </si>
+  <si>
+    <t>每次刷新出现的游客购买次数上限</t>
   </si>
   <si>
     <t>是否可以手动刷新</t>
@@ -284,6 +190,9 @@
     <t>boolean</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
@@ -302,7 +211,10 @@
     <t>visitorGiftPackCount</t>
   </si>
   <si>
-    <t>DailyRefresh</t>
+    <t>IsRefreshByTimePeriod</t>
+  </si>
+  <si>
+    <t>DailyRefreshTime</t>
   </si>
   <si>
     <t>DailyViewLimit</t>
@@ -311,7 +223,10 @@
     <t>RefreshCost</t>
   </si>
   <si>
-    <t>DailyRefreshLimit</t>
+    <t>MaxManualRefreshPerPeriod</t>
+  </si>
+  <si>
+    <t>MaxPurchasePerRefresh</t>
   </si>
   <si>
     <t>ManualRefresh</t>
@@ -326,25 +241,13 @@
     <t>付费卡池</t>
   </si>
   <si>
-    <t>1980000_0|1980000_20|1980000_30|1980000_40|1980000_50</t>
+    <t>0_6_10_14_19</t>
+  </si>
+  <si>
+    <t>1980000_20|1980000_30|1980000_40|1980000_50</t>
   </si>
   <si>
     <t>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
-  </si>
-  <si>
-    <t>是否按时段刷新</t>
-  </si>
-  <si>
-    <t>每日多长时间刷新一次（H)</t>
-  </si>
-  <si>
-    <t>每个时间段手动刷新的次数上限</t>
-  </si>
-  <si>
-    <t>每次刷新出现的游客购买次数上限</t>
-  </si>
-  <si>
-    <t>1980000_20|1980000_30|1980000_40|1980000_50</t>
   </si>
 </sst>
 </file>
@@ -357,7 +260,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,6 +272,13 @@
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -872,137 +782,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1015,10 +925,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1301,6 +1217,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1559,222 +1480,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
-  <cols>
-    <col min="4" max="5" width="16.375" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="19.25" customWidth="1"/>
-    <col min="9" max="9" width="59.375" customWidth="1"/>
-    <col min="10" max="10" width="20.625" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="22.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:12">
-      <c r="A5" s="3">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>10</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:12">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B5:B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
@@ -1782,7 +1487,7 @@
     <col min="5" max="5" width="16.375" customWidth="1"/>
     <col min="6" max="6" width="23.125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="8" max="8" width="17.875" customWidth="1"/>
     <col min="9" max="9" width="16.125" customWidth="1"/>
     <col min="10" max="10" width="16.25" customWidth="1"/>
     <col min="11" max="11" width="26.5" customWidth="1"/>
@@ -1810,102 +1515,110 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="M3" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -1929,11 +1642,11 @@
       <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1957,19 +1670,19 @@
       <c r="M5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>26</v>
+      <c r="N5" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:14">
       <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>27</v>
+      <c r="C6" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -1983,11 +1696,11 @@
       <c r="G6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="3">
-        <v>8</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
+      <c r="H6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="K6" s="3">
@@ -1999,8 +1712,8 @@
       <c r="M6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>29</v>
+      <c r="N6" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2013,7 +1726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="E5:G60"/>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -249,7 +249,7 @@
     <t>0_6_10_14_19</t>
   </si>
   <si>
-    <t>1980000_20|1980000_30|1980000_40|1980000_50</t>
+    <t>1980000_20|1980000_30|1980000_40|1980000_50|1980000_50</t>
   </si>
   <si>
     <t>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
@@ -436,12 +436,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -78,11 +78,12 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-指在礼包中可能出现的游客种类个数</t>
+指在礼包中可能出现的游客种类个数
+若是品质卡池，表示出现的那类卡池，购买后，那种品质的游客都可能出现，一种品质的游客为6个</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -117,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -140,12 +141,103 @@
         </r>
       </text>
     </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+在指定生成游客界面出现后，确定要出现的礼包/游客是啥</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+表明这个礼包在指定生成游客界面显示出来的概率
+空值/100表示必定出现；
+1-100表示具体的百分比概率</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+读取VisitorQualityAcquisition表中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+读取VisitorQualityAcquisition表中的ID
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>序号ID</t>
   </si>
@@ -162,6 +254,9 @@
     <t>界面显示的个数</t>
   </si>
   <si>
+    <t>是否开启</t>
+  </si>
+  <si>
     <t>礼包出现游客的种类个数</t>
   </si>
   <si>
@@ -189,6 +284,9 @@
     <t>出现的游客_权重</t>
   </si>
   <si>
+    <t>礼包出现的概率(百分比）</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -213,6 +311,9 @@
     <t>DisplayCount</t>
   </si>
   <si>
+    <t>IsEnabled</t>
+  </si>
+  <si>
     <t>visitorGiftPackCount</t>
   </si>
   <si>
@@ -237,6 +338,12 @@
     <t>ManualRefresh</t>
   </si>
   <si>
+    <t>VisitorWeight</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
     <t>广告卡池</t>
   </si>
   <si>
@@ -253,6 +360,24 @@
   </si>
   <si>
     <t>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
+  </si>
+  <si>
+    <t>品质卡池1</t>
+  </si>
+  <si>
+    <t>10001_100|20001_100|30001_100</t>
+  </si>
+  <si>
+    <t>品质卡池2</t>
+  </si>
+  <si>
+    <t>0_6_10_14_20</t>
+  </si>
+  <si>
+    <t>1980000_20|1980000_30|1980000_40|1980000_50|1980000_51</t>
+  </si>
+  <si>
+    <t>40001_100|50001_100</t>
   </si>
 </sst>
 </file>
@@ -436,12 +561,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -646,7 +771,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -661,6 +786,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -793,7 +931,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -805,34 +943,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -917,7 +1055,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -939,11 +1077,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1485,23 +1629,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="4" max="4" width="11.125" customWidth="1"/>
     <col min="5" max="5" width="16.375" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-    <col min="9" max="9" width="16.125" customWidth="1"/>
-    <col min="10" max="10" width="16.25" customWidth="1"/>
-    <col min="11" max="11" width="26.5" customWidth="1"/>
-    <col min="12" max="12" width="30.125" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="22.875" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="23.125" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="16.25" customWidth="1"/>
+    <col min="12" max="12" width="26.5" customWidth="1"/>
+    <col min="13" max="13" width="30.125" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="22.875" customWidth="1"/>
+    <col min="16" max="16" width="14.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1520,114 +1666,134 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="K3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1642,16 +1808,18 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:14">
+      <c r="O4" s="7"/>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:16">
       <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>30</v>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1659,35 +1827,39 @@
       <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="b">
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
         <v>10</v>
       </c>
-      <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="3" t="b">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:14">
+      <c r="O5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:16">
       <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>32</v>
+      <c r="C6" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -1695,34 +1867,134 @@
       <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="b">
+      <c r="H6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="I6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="3">
         <v>4</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>1</v>
       </c>
-      <c r="M6" s="3" t="b">
+      <c r="N6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="9" t="s">
-        <v>35</v>
+      <c r="O6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:16">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8">
+        <v>3</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="3">
+        <v>4</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="N7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:16">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="3">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="6">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B6">
+  <conditionalFormatting sqref="B5:B8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -83,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -110,41 +110,6 @@
       <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>当配置的消耗低于刷新的次数时，配置的最后那个消耗一直重复使用</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--1或空值表示没有上限；
-具体值时为对应值的次数上限</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
@@ -163,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -187,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O7" authorId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -209,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0">
+    <comment ref="K8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -237,7 +202,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>序号ID</t>
   </si>
@@ -263,21 +228,9 @@
     <t>是否按时段刷新</t>
   </si>
   <si>
-    <t>每日的刷新时间点</t>
-  </si>
-  <si>
     <t>单日观看次数上限</t>
   </si>
   <si>
-    <t>手动刷新的费用</t>
-  </si>
-  <si>
-    <t>每个时间段手动刷新的次数上限</t>
-  </si>
-  <si>
-    <t>每次刷新出现的游客购买次数上限</t>
-  </si>
-  <si>
     <t>是否可以手动刷新</t>
   </si>
   <si>
@@ -293,9 +246,6 @@
     <t>boolean</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{_}</t>
-  </si>
-  <si>
     <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
@@ -320,21 +270,9 @@
     <t>IsRefreshByTimePeriod</t>
   </si>
   <si>
-    <t>DailyRefreshTime</t>
-  </si>
-  <si>
     <t>DailyViewLimit</t>
   </si>
   <si>
-    <t>RefreshCost</t>
-  </si>
-  <si>
-    <t>MaxManualRefreshPerPeriod</t>
-  </si>
-  <si>
-    <t>MaxPurchasePerRefresh</t>
-  </si>
-  <si>
     <t>ManualRefresh</t>
   </si>
   <si>
@@ -353,12 +291,6 @@
     <t>付费卡池</t>
   </si>
   <si>
-    <t>0_6_10_14_19</t>
-  </si>
-  <si>
-    <t>1980000_20|1980000_30|1980000_40|1980000_50|1980000_50</t>
-  </si>
-  <si>
     <t>1025101_500|1025102_500|1025103_500|1025104_500|1025105_500|1025106_500|1025201_400|1025202_400|1025203_400|1025204_400|1025205_400|1025206_400|1025301_300|1025302_300|1025303_300|1025304_300|1025305_300|1025306_300|1025401_200|1025402_200|1025403_200|1025404_200|1025405_200|1025406_200|1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
   </si>
   <si>
@@ -369,12 +301,6 @@
   </si>
   <si>
     <t>品质卡池2</t>
-  </si>
-  <si>
-    <t>0_6_10_14_20</t>
-  </si>
-  <si>
-    <t>1980000_20|1980000_30|1980000_40|1980000_50|1980000_51</t>
   </si>
   <si>
     <t>40001_100|50001_100</t>
@@ -390,7 +316,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,12 +335,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -571,11 +491,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -925,137 +840,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1071,16 +986,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1629,7 +1538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="4" max="4" width="11.125" customWidth="1"/>
@@ -1637,17 +1546,13 @@
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="23.125" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="17.875" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="16.25" customWidth="1"/>
-    <col min="12" max="12" width="26.5" customWidth="1"/>
-    <col min="13" max="13" width="30.125" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="22.875" customWidth="1"/>
-    <col min="16" max="16" width="14.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="16.125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="22.875" customWidth="1"/>
+    <col min="12" max="12" width="14.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1675,125 +1580,89 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1804,22 +1673,18 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:16">
+      <c r="K4" s="6"/>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
+      <c r="C5" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1836,30 +1701,26 @@
       <c r="H5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="3">
         <v>10</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3" t="b">
+      <c r="J5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" ht="16.5" spans="1:16">
+      <c r="K5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>37</v>
+      <c r="C6" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -1876,36 +1737,24 @@
       <c r="H6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="3">
-        <v>4</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="I6" s="9"/>
+      <c r="J6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:16">
+      <c r="K6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>41</v>
+      <c r="C7" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -1922,38 +1771,26 @@
       <c r="H7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="3">
-        <v>4</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="I7" s="5"/>
+      <c r="J7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" s="6">
+      <c r="K7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:16">
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="8">
-        <v>4</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>43</v>
+      <c r="B8" s="7">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1970,26 +1807,14 @@
       <c r="H8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="3">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="I8" s="5"/>
+      <c r="J8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="6">
+      <c r="K8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="5">
         <v>50</v>
       </c>
     </row>

--- a/hall/resources/sample/VisitorTargetList.xlsx
+++ b/hall/resources/sample/VisitorTargetList.xlsx
@@ -249,7 +249,7 @@
     <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>id</t>
   </si>
   <si>
     <t>PoolType</t>
